--- a/ABA_mining/outputs/task3/llama3.2/contrary_v6/check-in/task3_contrary_v6_check-in_ALL_sheets.xlsx
+++ b/ABA_mining/outputs/task3/llama3.2/contrary_v6/check-in/task3_contrary_v6_check-in_ALL_sheets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>Test 1</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +503,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +564,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +625,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -646,6 +686,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -697,6 +747,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -748,6 +808,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -799,6 +869,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -850,6 +930,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -901,6 +991,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -952,6 +1052,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1003,6 +1113,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1054,6 +1174,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1105,6 +1235,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1156,6 +1296,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1207,6 +1357,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1258,6 +1418,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1309,6 +1479,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1360,6 +1540,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1411,6 +1601,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1462,6 +1662,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1513,6 +1723,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1564,6 +1784,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1615,6 +1845,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1666,6 +1906,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1717,6 +1967,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1768,6 +2028,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1819,6 +2089,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1870,6 +2150,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1921,6 +2211,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1972,6 +2272,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2023,6 +2333,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2074,6 +2394,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2125,6 +2455,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2176,6 +2516,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2227,6 +2577,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2278,6 +2638,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2329,6 +2699,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2380,6 +2760,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2431,6 +2821,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2482,6 +2882,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2533,6 +2943,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2584,6 +3004,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2635,6 +3065,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2686,6 +3126,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2737,6 +3187,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2788,6 +3248,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2839,6 +3309,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2890,6 +3370,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2941,6 +3431,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2992,6 +3492,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3043,6 +3553,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3094,6 +3614,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3145,6 +3675,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3196,6 +3736,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3247,6 +3797,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3298,6 +3858,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3349,6 +3919,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3400,6 +3980,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3451,6 +4041,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3502,6 +4102,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3553,6 +4163,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3604,6 +4224,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3655,6 +4285,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3706,6 +4346,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3757,6 +4407,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3808,6 +4468,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3859,6 +4529,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3910,6 +4590,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3961,6 +4651,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4012,6 +4712,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4063,6 +4773,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4114,6 +4834,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4165,6 +4895,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4216,6 +4956,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4267,6 +5017,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4318,6 +5078,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4369,6 +5139,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4420,6 +5200,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4471,6 +5261,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4522,6 +5322,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4573,6 +5383,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4624,6 +5444,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4675,6 +5505,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4726,6 +5566,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4777,6 +5627,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4828,6 +5688,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4879,6 +5749,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4930,6 +5810,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4981,6 +5871,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5032,6 +5932,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5083,6 +5993,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5134,6 +6054,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5185,6 +6115,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5236,6 +6176,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5287,6 +6237,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5338,6 +6298,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5389,6 +6359,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5440,6 +6420,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5491,6 +6481,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5542,6 +6542,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5593,6 +6603,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5644,6 +6664,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5695,6 +6725,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5746,6 +6786,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5797,6 +6847,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5848,6 +6908,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5899,6 +6969,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5950,6 +7030,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6001,6 +7091,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6052,6 +7152,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6103,6 +7213,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6154,6 +7274,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6205,6 +7335,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6256,6 +7396,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6307,6 +7457,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6358,6 +7518,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6409,6 +7579,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6460,6 +7640,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6511,6 +7701,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6562,6 +7762,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6613,6 +7823,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6664,6 +7884,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6715,6 +7945,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6766,6 +8006,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6817,6 +8067,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6868,6 +8128,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6919,6 +8189,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6970,6 +8250,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7021,6 +8311,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7072,6 +8372,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7123,6 +8433,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7174,6 +8494,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7225,6 +8555,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7276,6 +8616,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7327,6 +8677,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7378,6 +8738,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7429,6 +8799,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7480,6 +8860,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7531,6 +8921,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7582,6 +8982,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7633,6 +9043,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7684,6 +9104,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7735,6 +9165,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7786,6 +9226,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7837,6 +9287,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7888,6 +9348,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7939,6 +9409,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7990,6 +9470,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8041,6 +9531,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8092,6 +9592,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8143,6 +9653,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8194,6 +9714,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8245,6 +9775,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8296,6 +9836,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8347,6 +9897,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8398,6 +9958,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8449,6 +10019,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8500,6 +10080,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8551,6 +10141,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8602,6 +10202,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8653,6 +10263,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8704,6 +10324,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8755,6 +10385,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8806,6 +10446,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8857,6 +10507,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8908,6 +10568,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8959,6 +10629,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9010,6 +10690,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9061,6 +10751,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9112,6 +10812,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9163,6 +10873,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9214,6 +10934,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9265,6 +10995,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9316,6 +11056,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9367,6 +11117,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9418,6 +11178,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9469,6 +11239,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9520,6 +11300,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9571,6 +11361,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9622,6 +11422,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9673,6 +11483,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9724,6 +11544,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9775,6 +11605,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9826,6 +11666,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9877,6 +11727,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9928,6 +11788,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9979,6 +11849,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10030,6 +11910,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10081,6 +11971,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10132,6 +12032,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10183,6 +12093,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10234,6 +12154,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10285,6 +12215,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10336,6 +12276,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10387,6 +12337,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10438,6 +12398,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10489,6 +12459,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10540,6 +12520,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10591,6 +12581,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10642,6 +12642,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10693,6 +12703,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10744,6 +12764,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10795,6 +12825,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10846,6 +12886,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10897,6 +12947,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10948,6 +13008,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10999,6 +13069,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11050,6 +13130,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11101,6 +13191,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11152,6 +13252,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11203,6 +13313,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11254,6 +13374,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11305,6 +13435,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11356,6 +13496,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11407,6 +13557,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11458,6 +13618,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11509,6 +13679,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11560,6 +13740,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11611,6 +13801,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11662,6 +13862,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11713,6 +13923,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11764,6 +13984,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11815,6 +14045,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11866,6 +14106,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11917,6 +14167,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11968,6 +14228,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12019,6 +14289,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12070,6 +14350,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12121,6 +14411,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12172,6 +14472,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12223,6 +14533,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12274,6 +14594,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12325,6 +14655,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12376,6 +14716,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12427,6 +14777,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12478,6 +14838,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12529,6 +14899,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12580,6 +14960,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12631,6 +15021,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12682,6 +15082,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12733,6 +15143,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12784,6 +15204,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12835,6 +15265,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12886,6 +15326,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12937,6 +15387,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12988,6 +15448,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13039,6 +15509,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13090,6 +15570,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13141,6 +15631,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13192,6 +15692,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13243,6 +15753,16 @@
           <t>No</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13290,6 +15810,16 @@
         </is>
       </c>
       <c r="E253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
         <is>
           <t>No</t>
         </is>
